--- a/src/report/assets/downgrade_base.xlsx
+++ b/src/report/assets/downgrade_base.xlsx
@@ -132,7 +132,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -256,11 +256,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -337,6 +351,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -976,18 +1002,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="12" customWidth="1" style="14" min="1" max="1"/>
-    <col width="22" customWidth="1" style="14" min="2" max="2"/>
-    <col width="9" customWidth="1" style="14" min="3" max="3"/>
-    <col width="13" customWidth="1" style="14" min="4" max="5"/>
-    <col width="11" customWidth="1" style="14" min="6" max="6"/>
+    <col width="6" customWidth="1" style="14" min="1" max="1"/>
+    <col width="12" customWidth="1" style="14" min="2" max="2"/>
+    <col width="22" customWidth="1" style="14" min="3" max="3"/>
+    <col width="9" customWidth="1" style="14" min="4" max="5"/>
+    <col width="13" customWidth="1" style="14" min="5" max="5"/>
+    <col width="13" customWidth="1" style="14" min="6" max="6"/>
+    <col width="11" customWidth="1" style="14" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="14">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>阜阳分行“降级挽回”网点明细（MMDD-MMDD）</t>
         </is>
@@ -996,374 +1024,421 @@
     <row r="2" ht="14.5" customHeight="1" s="14">
       <c r="A2" s="10" t="inlineStr">
         <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
           <t>支行</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>网点</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>客户数</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>资产提升额</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>存款提升额</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>综合评价</t>
         </is>
       </c>
     </row>
     <row r="3" ht="14.5" customHeight="1" s="14">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="23" t="n"/>
-      <c r="E3" s="23" t="n"/>
-      <c r="F3" s="23" t="n"/>
+      <c r="A3" s="30" t="n"/>
+      <c r="B3" s="31" t="n"/>
+      <c r="C3" s="32" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
     </row>
     <row r="4" ht="14.5" customHeight="1" s="14">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="23" t="n"/>
-      <c r="D4" s="23" t="n"/>
-      <c r="E4" s="23" t="n"/>
-      <c r="F4" s="23" t="n"/>
+      <c r="A4" s="30" t="n"/>
+      <c r="B4" s="31" t="n"/>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
     </row>
     <row r="5" ht="14.5" customHeight="1" s="14">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
-      <c r="F5" s="23" t="n"/>
+      <c r="A5" s="30" t="n"/>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
     </row>
     <row r="6" ht="14.5" customHeight="1" s="14">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="23" t="n"/>
-      <c r="E6" s="23" t="n"/>
-      <c r="F6" s="23" t="n"/>
+      <c r="A6" s="30" t="n"/>
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
     </row>
     <row r="7" ht="14.5" customHeight="1" s="14">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="23" t="n"/>
-      <c r="F7" s="23" t="n"/>
+      <c r="A7" s="30" t="n"/>
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="33" t="n"/>
+      <c r="E7" s="33" t="n"/>
+      <c r="F7" s="33" t="n"/>
+      <c r="G7" s="33" t="n"/>
     </row>
     <row r="8" ht="14.5" customHeight="1" s="14">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="23" t="n"/>
-      <c r="D8" s="23" t="n"/>
-      <c r="E8" s="23" t="n"/>
-      <c r="F8" s="23" t="n"/>
+      <c r="A8" s="30" t="n"/>
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="32" t="n"/>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="33" t="n"/>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="33" t="n"/>
     </row>
     <row r="9" ht="14.5" customHeight="1" s="14">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="23" t="n"/>
-      <c r="D9" s="23" t="n"/>
-      <c r="E9" s="23" t="n"/>
-      <c r="F9" s="23" t="n"/>
+      <c r="A9" s="30" t="n"/>
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="32" t="n"/>
+      <c r="D9" s="33" t="n"/>
+      <c r="E9" s="33" t="n"/>
+      <c r="F9" s="33" t="n"/>
+      <c r="G9" s="33" t="n"/>
     </row>
     <row r="10" ht="14.5" customHeight="1" s="14">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="23" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="23" t="n"/>
-      <c r="F10" s="23" t="n"/>
+      <c r="A10" s="30" t="n"/>
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33" t="n"/>
+      <c r="E10" s="33" t="n"/>
+      <c r="F10" s="33" t="n"/>
+      <c r="G10" s="33" t="n"/>
     </row>
     <row r="11" ht="14.5" customHeight="1" s="14">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="n"/>
-      <c r="F11" s="23" t="n"/>
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33" t="n"/>
+      <c r="E11" s="33" t="n"/>
+      <c r="F11" s="33" t="n"/>
+      <c r="G11" s="33" t="n"/>
     </row>
     <row r="12" ht="14.5" customHeight="1" s="14">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="23" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="n"/>
+      <c r="A12" s="30" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33" t="n"/>
+      <c r="E12" s="33" t="n"/>
+      <c r="F12" s="33" t="n"/>
+      <c r="G12" s="33" t="n"/>
     </row>
     <row r="13" ht="14.5" customHeight="1" s="14">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="n"/>
+      <c r="A13" s="30" t="n"/>
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33" t="n"/>
+      <c r="E13" s="33" t="n"/>
+      <c r="F13" s="33" t="n"/>
+      <c r="G13" s="33" t="n"/>
     </row>
     <row r="14" ht="14.5" customHeight="1" s="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="23" t="n"/>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="23" t="n"/>
-      <c r="F14" s="23" t="n"/>
+      <c r="A14" s="30" t="n"/>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="32" t="n"/>
+      <c r="D14" s="33" t="n"/>
+      <c r="E14" s="33" t="n"/>
+      <c r="F14" s="33" t="n"/>
+      <c r="G14" s="33" t="n"/>
     </row>
     <row r="15" ht="14.5" customHeight="1" s="14">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="23" t="n"/>
-      <c r="F15" s="23" t="n"/>
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="32" t="n"/>
+      <c r="D15" s="33" t="n"/>
+      <c r="E15" s="33" t="n"/>
+      <c r="F15" s="33" t="n"/>
+      <c r="G15" s="33" t="n"/>
     </row>
     <row r="16" ht="14.5" customHeight="1" s="14">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="23" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="23" t="n"/>
-      <c r="F16" s="23" t="n"/>
+      <c r="A16" s="30" t="n"/>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33" t="n"/>
+      <c r="E16" s="33" t="n"/>
+      <c r="F16" s="33" t="n"/>
+      <c r="G16" s="33" t="n"/>
     </row>
     <row r="17" ht="14.5" customHeight="1" s="14">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="23" t="n"/>
-      <c r="D17" s="23" t="n"/>
-      <c r="E17" s="23" t="n"/>
-      <c r="F17" s="23" t="n"/>
+      <c r="A17" s="30" t="n"/>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33" t="n"/>
+      <c r="E17" s="33" t="n"/>
+      <c r="F17" s="33" t="n"/>
+      <c r="G17" s="33" t="n"/>
     </row>
     <row r="18" ht="14.5" customHeight="1" s="14">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="23" t="n"/>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="23" t="n"/>
-      <c r="F18" s="23" t="n"/>
+      <c r="A18" s="30" t="n"/>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33" t="n"/>
+      <c r="E18" s="33" t="n"/>
+      <c r="F18" s="33" t="n"/>
+      <c r="G18" s="33" t="n"/>
     </row>
     <row r="19" ht="14.5" customHeight="1" s="14">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="23" t="n"/>
-      <c r="D19" s="23" t="n"/>
-      <c r="E19" s="23" t="n"/>
-      <c r="F19" s="23" t="n"/>
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33" t="n"/>
+      <c r="E19" s="33" t="n"/>
+      <c r="F19" s="33" t="n"/>
+      <c r="G19" s="33" t="n"/>
     </row>
     <row r="20" ht="14.5" customHeight="1" s="14">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="23" t="n"/>
-      <c r="F20" s="23" t="n"/>
+      <c r="A20" s="30" t="n"/>
+      <c r="B20" s="31" t="n"/>
+      <c r="C20" s="32" t="n"/>
+      <c r="D20" s="33" t="n"/>
+      <c r="E20" s="33" t="n"/>
+      <c r="F20" s="33" t="n"/>
+      <c r="G20" s="33" t="n"/>
     </row>
     <row r="21" ht="14.5" customHeight="1" s="14">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="23" t="n"/>
-      <c r="F21" s="23" t="n"/>
+      <c r="A21" s="30" t="n"/>
+      <c r="B21" s="31" t="n"/>
+      <c r="C21" s="32" t="n"/>
+      <c r="D21" s="33" t="n"/>
+      <c r="E21" s="33" t="n"/>
+      <c r="F21" s="33" t="n"/>
+      <c r="G21" s="33" t="n"/>
     </row>
     <row r="22" ht="14.5" customHeight="1" s="14">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="23" t="n"/>
-      <c r="F22" s="23" t="n"/>
+      <c r="A22" s="30" t="n"/>
+      <c r="B22" s="31" t="n"/>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33" t="n"/>
+      <c r="E22" s="33" t="n"/>
+      <c r="F22" s="33" t="n"/>
+      <c r="G22" s="33" t="n"/>
     </row>
     <row r="23" ht="14.5" customHeight="1" s="14">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="23" t="n"/>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="23" t="n"/>
-      <c r="F23" s="23" t="n"/>
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="31" t="n"/>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33" t="n"/>
+      <c r="E23" s="33" t="n"/>
+      <c r="F23" s="33" t="n"/>
+      <c r="G23" s="33" t="n"/>
     </row>
     <row r="24" ht="14.5" customHeight="1" s="14">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n"/>
-      <c r="F24" s="23" t="n"/>
+      <c r="A24" s="30" t="n"/>
+      <c r="B24" s="31" t="n"/>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="33" t="n"/>
+      <c r="G24" s="33" t="n"/>
     </row>
     <row r="25" ht="14.5" customHeight="1" s="14">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="23" t="n"/>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="23" t="n"/>
-      <c r="F25" s="23" t="n"/>
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="31" t="n"/>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33" t="n"/>
+      <c r="E25" s="33" t="n"/>
+      <c r="F25" s="33" t="n"/>
+      <c r="G25" s="33" t="n"/>
     </row>
     <row r="26" ht="14.5" customHeight="1" s="14">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n"/>
-      <c r="F26" s="23" t="n"/>
+      <c r="A26" s="30" t="n"/>
+      <c r="B26" s="31" t="n"/>
+      <c r="C26" s="32" t="n"/>
+      <c r="D26" s="33" t="n"/>
+      <c r="E26" s="33" t="n"/>
+      <c r="F26" s="33" t="n"/>
+      <c r="G26" s="33" t="n"/>
     </row>
     <row r="27" ht="14.5" customHeight="1" s="14">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="23" t="n"/>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="23" t="n"/>
-      <c r="F27" s="23" t="n"/>
+      <c r="A27" s="30" t="n"/>
+      <c r="B27" s="31" t="n"/>
+      <c r="C27" s="32" t="n"/>
+      <c r="D27" s="33" t="n"/>
+      <c r="E27" s="33" t="n"/>
+      <c r="F27" s="33" t="n"/>
+      <c r="G27" s="33" t="n"/>
     </row>
     <row r="28" ht="14.5" customHeight="1" s="14">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="23" t="n"/>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="23" t="n"/>
-      <c r="F28" s="23" t="n"/>
+      <c r="A28" s="30" t="n"/>
+      <c r="B28" s="31" t="n"/>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33" t="n"/>
+      <c r="E28" s="33" t="n"/>
+      <c r="F28" s="33" t="n"/>
+      <c r="G28" s="33" t="n"/>
     </row>
     <row r="29" ht="14.5" customHeight="1" s="14">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="23" t="n"/>
-      <c r="F29" s="23" t="n"/>
+      <c r="A29" s="30" t="n"/>
+      <c r="B29" s="31" t="n"/>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33" t="n"/>
+      <c r="E29" s="33" t="n"/>
+      <c r="F29" s="33" t="n"/>
+      <c r="G29" s="33" t="n"/>
     </row>
     <row r="30" ht="14.5" customHeight="1" s="14">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="23" t="n"/>
-      <c r="E30" s="23" t="n"/>
-      <c r="F30" s="23" t="n"/>
+      <c r="A30" s="30" t="n"/>
+      <c r="B30" s="31" t="n"/>
+      <c r="C30" s="32" t="n"/>
+      <c r="D30" s="33" t="n"/>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="33" t="n"/>
+      <c r="G30" s="33" t="n"/>
     </row>
     <row r="31" ht="14.5" customHeight="1" s="14">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="23" t="n"/>
-      <c r="E31" s="23" t="n"/>
-      <c r="F31" s="23" t="n"/>
+      <c r="A31" s="30" t="n"/>
+      <c r="B31" s="31" t="n"/>
+      <c r="C31" s="32" t="n"/>
+      <c r="D31" s="33" t="n"/>
+      <c r="E31" s="33" t="n"/>
+      <c r="F31" s="33" t="n"/>
+      <c r="G31" s="33" t="n"/>
     </row>
     <row r="32" ht="14.5" customHeight="1" s="14">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="23" t="n"/>
-      <c r="E32" s="23" t="n"/>
-      <c r="F32" s="23" t="n"/>
+      <c r="A32" s="30" t="n"/>
+      <c r="B32" s="31" t="n"/>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33" t="n"/>
+      <c r="E32" s="33" t="n"/>
+      <c r="F32" s="33" t="n"/>
+      <c r="G32" s="33" t="n"/>
     </row>
     <row r="33" ht="14.5" customHeight="1" s="14">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="23" t="n"/>
-      <c r="E33" s="23" t="n"/>
-      <c r="F33" s="23" t="n"/>
+      <c r="A33" s="30" t="n"/>
+      <c r="B33" s="31" t="n"/>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33" t="n"/>
+      <c r="E33" s="33" t="n"/>
+      <c r="F33" s="33" t="n"/>
+      <c r="G33" s="33" t="n"/>
     </row>
     <row r="34" ht="14.5" customHeight="1" s="14">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="23" t="n"/>
-      <c r="F34" s="23" t="n"/>
+      <c r="A34" s="30" t="n"/>
+      <c r="B34" s="31" t="n"/>
+      <c r="C34" s="32" t="n"/>
+      <c r="D34" s="33" t="n"/>
+      <c r="E34" s="33" t="n"/>
+      <c r="F34" s="33" t="n"/>
+      <c r="G34" s="33" t="n"/>
     </row>
     <row r="35" ht="14.5" customHeight="1" s="14">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="23" t="n"/>
-      <c r="E35" s="23" t="n"/>
-      <c r="F35" s="23" t="n"/>
+      <c r="A35" s="30" t="n"/>
+      <c r="B35" s="31" t="n"/>
+      <c r="C35" s="32" t="n"/>
+      <c r="D35" s="33" t="n"/>
+      <c r="E35" s="33" t="n"/>
+      <c r="F35" s="33" t="n"/>
+      <c r="G35" s="33" t="n"/>
     </row>
     <row r="36" ht="14.5" customHeight="1" s="14">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="23" t="n"/>
-      <c r="F36" s="23" t="n"/>
+      <c r="A36" s="30" t="n"/>
+      <c r="B36" s="31" t="n"/>
+      <c r="C36" s="32" t="n"/>
+      <c r="D36" s="33" t="n"/>
+      <c r="E36" s="33" t="n"/>
+      <c r="F36" s="33" t="n"/>
+      <c r="G36" s="33" t="n"/>
     </row>
     <row r="37" ht="14.5" customHeight="1" s="14">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="23" t="n"/>
-      <c r="E37" s="23" t="n"/>
-      <c r="F37" s="23" t="n"/>
+      <c r="A37" s="30" t="n"/>
+      <c r="B37" s="31" t="n"/>
+      <c r="C37" s="32" t="n"/>
+      <c r="D37" s="33" t="n"/>
+      <c r="E37" s="33" t="n"/>
+      <c r="F37" s="33" t="n"/>
+      <c r="G37" s="33" t="n"/>
     </row>
     <row r="38" ht="14.5" customHeight="1" s="14">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="23" t="n"/>
-      <c r="E38" s="23" t="n"/>
-      <c r="F38" s="23" t="n"/>
+      <c r="A38" s="30" t="n"/>
+      <c r="B38" s="31" t="n"/>
+      <c r="C38" s="32" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
+      <c r="G38" s="33" t="n"/>
     </row>
     <row r="39" ht="14.5" customHeight="1" s="14">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="23" t="n"/>
-      <c r="D39" s="23" t="n"/>
-      <c r="E39" s="23" t="n"/>
-      <c r="F39" s="23" t="n"/>
+      <c r="A39" s="30" t="n"/>
+      <c r="B39" s="31" t="n"/>
+      <c r="C39" s="32" t="n"/>
+      <c r="D39" s="33" t="n"/>
+      <c r="E39" s="33" t="n"/>
+      <c r="F39" s="33" t="n"/>
+      <c r="G39" s="33" t="n"/>
     </row>
     <row r="40" ht="14.5" customHeight="1" s="14">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="23" t="n"/>
-      <c r="D40" s="23" t="n"/>
-      <c r="E40" s="23" t="n"/>
-      <c r="F40" s="23" t="n"/>
+      <c r="A40" s="30" t="n"/>
+      <c r="B40" s="31" t="n"/>
+      <c r="C40" s="32" t="n"/>
+      <c r="D40" s="33" t="n"/>
+      <c r="E40" s="33" t="n"/>
+      <c r="F40" s="33" t="n"/>
+      <c r="G40" s="33" t="n"/>
     </row>
     <row r="41" ht="14.5" customHeight="1" s="14">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="23" t="n"/>
-      <c r="D41" s="23" t="n"/>
-      <c r="E41" s="23" t="n"/>
-      <c r="F41" s="23" t="n"/>
+      <c r="A41" s="30" t="n"/>
+      <c r="B41" s="31" t="n"/>
+      <c r="C41" s="32" t="n"/>
+      <c r="D41" s="33" t="n"/>
+      <c r="E41" s="33" t="n"/>
+      <c r="F41" s="33" t="n"/>
+      <c r="G41" s="33" t="n"/>
     </row>
     <row r="42" ht="14.5" customHeight="1" s="14">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="23" t="n"/>
-      <c r="D42" s="23" t="n"/>
-      <c r="E42" s="23" t="n"/>
-      <c r="F42" s="23" t="n"/>
+      <c r="A42" s="30" t="n"/>
+      <c r="B42" s="31" t="n"/>
+      <c r="C42" s="32" t="n"/>
+      <c r="D42" s="33" t="n"/>
+      <c r="E42" s="33" t="n"/>
+      <c r="F42" s="33" t="n"/>
+      <c r="G42" s="33" t="n"/>
     </row>
     <row r="43" ht="14.5" customHeight="1" s="14">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
+      <c r="A43" s="30" t="n"/>
+      <c r="B43" s="31" t="n"/>
+      <c r="C43" s="32" t="n"/>
+      <c r="D43" s="31" t="n"/>
+      <c r="E43" s="31" t="n"/>
+      <c r="F43" s="31" t="n"/>
+      <c r="G43" s="31" t="n"/>
     </row>
     <row r="44" ht="14.5" customHeight="1" s="14">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
+      <c r="A44" s="30" t="n"/>
+      <c r="B44" s="31" t="n"/>
+      <c r="C44" s="32" t="n"/>
+      <c r="D44" s="31" t="n"/>
+      <c r="E44" s="31" t="n"/>
+      <c r="F44" s="31" t="n"/>
+      <c r="G44" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
